--- a/자리배치명단(양식).xlsx
+++ b/자리배치명단(양식).xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="학생명단" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,70 +448,310 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>성별</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>남</t>
-        </is>
-      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>여</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
